--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2022_valparaiso.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2022_valparaiso.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:09</t>
+    <t xml:space="preserve">2026-09-09 19:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2022_valparaiso.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2022_valparaiso.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:41</t>
+    <t xml:space="preserve">2026-09-17 04:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2022_valparaiso.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2022_valparaiso.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 04:07</t>
+    <t xml:space="preserve">2026-09-27 02:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2022_valparaiso.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2022_valparaiso.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 02:35</t>
+    <t xml:space="preserve">2026-10-03 01:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2022_valparaiso.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2022_valparaiso.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t xml:space="preserve">Territorio</t>
   </si>
@@ -35,7 +35,7 @@
     <t xml:space="preserve">apoyo</t>
   </si>
   <si>
-    <t xml:space="preserve">Valparaiso</t>
+    <t xml:space="preserve">Valparaíso</t>
   </si>
   <si>
     <t xml:space="preserve">Campo</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-03 01:34</t>
+    <t xml:space="preserve">2026-10-05 05:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Region de Valparaiso</t>
+    <t xml:space="preserve">Region de Valparaíso</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
@@ -102,9 +102,6 @@
   </si>
   <si>
     <t xml:space="preserve">Provincia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valparaíso</t>
   </si>
   <si>
     <t xml:space="preserve">Isla de Pascua</t>
@@ -841,7 +838,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>25.48</v>
@@ -855,7 +852,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>31.69</v>
@@ -869,7 +866,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>29.14</v>
@@ -883,7 +880,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>28.17</v>
@@ -897,7 +894,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>28.39</v>
@@ -911,7 +908,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>28.58</v>
@@ -925,7 +922,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>29.23</v>
@@ -939,7 +936,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>27.33</v>
